--- a/E/CON02D.xlsx
+++ b/E/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="343">
   <si>
     <t/>
   </si>
@@ -94,6 +94,15 @@
     <t>CHA CHA SURPRISE 2'S</t>
   </si>
   <si>
+    <t>20143070</t>
+  </si>
+  <si>
+    <t>CHA CHA TSUM 2X12.5</t>
+  </si>
+  <si>
+    <t>TG,(E-1B)</t>
+  </si>
+  <si>
     <t>20097984</t>
   </si>
   <si>
@@ -106,6 +115,207 @@
     <t>CHOKI CHOKI CHO 4X9G</t>
   </si>
   <si>
+    <t>20141002</t>
+  </si>
+  <si>
+    <t>WONHAE MTCHA BRY 30G</t>
+  </si>
+  <si>
+    <t>20139890</t>
+  </si>
+  <si>
+    <t>WNHAE STRW CHEESCAKE</t>
+  </si>
+  <si>
+    <t>20139889</t>
+  </si>
+  <si>
+    <t>WNHAE PISTACHIO CHOC</t>
+  </si>
+  <si>
+    <t>20135198</t>
+  </si>
+  <si>
+    <t>WONHAE YOG.GUM ORI48</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20135661</t>
+  </si>
+  <si>
+    <t>WNHAE GMMY MXD.FRT32</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20143073</t>
+  </si>
+  <si>
+    <t>HIFRT GREN GRP PCK25</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20033392</t>
+  </si>
+  <si>
+    <t>DELFI CHACHA MINIS25</t>
+  </si>
+  <si>
+    <t>20077110</t>
+  </si>
+  <si>
+    <t>CHACHA MINIS HATS 25</t>
+  </si>
+  <si>
+    <t>20122057</t>
+  </si>
+  <si>
+    <t>CHACHA MINIS CAR12.5</t>
+  </si>
+  <si>
+    <t>20143071</t>
+  </si>
+  <si>
+    <t>CHA CHA DISNEY 25</t>
+  </si>
+  <si>
+    <t>20140016</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHO PEANUT 37G</t>
+  </si>
+  <si>
+    <t>20140013</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHOC CRSPY 30G</t>
+  </si>
+  <si>
+    <t>20129814</t>
+  </si>
+  <si>
+    <t>MLKITA CNDY BTES 24G</t>
+  </si>
+  <si>
+    <t>20140908</t>
+  </si>
+  <si>
+    <t>MLKITA PUDD STRW 85G</t>
+  </si>
+  <si>
+    <t>20140907</t>
+  </si>
+  <si>
+    <t>MLKITA PUDD MILK 85G</t>
+  </si>
+  <si>
+    <t>20136282</t>
+  </si>
+  <si>
+    <t>MILKITA LOLIPOP 3'S</t>
+  </si>
+  <si>
+    <t>20045175</t>
+  </si>
+  <si>
+    <t>CHA CHA MILK CHO 20G</t>
+  </si>
+  <si>
+    <t>20142588</t>
+  </si>
+  <si>
+    <t>CHA CHA PNUT CHO2X35</t>
+  </si>
+  <si>
+    <t>20063093</t>
+  </si>
+  <si>
+    <t>DELFI MALTITOS 26</t>
+  </si>
+  <si>
+    <t>10000418</t>
+  </si>
+  <si>
+    <t>DELFI CHIC CHOC 36G</t>
+  </si>
+  <si>
+    <t>20024539</t>
+  </si>
+  <si>
+    <t>S/Q BITES ALMOND 30G</t>
+  </si>
+  <si>
+    <t>20140906</t>
+  </si>
+  <si>
+    <t>MILKITA BAR CHOC 15G</t>
+  </si>
+  <si>
+    <t>20140412</t>
+  </si>
+  <si>
+    <t>MILKITA MILKY BAR 15</t>
+  </si>
+  <si>
+    <t>20113490</t>
+  </si>
+  <si>
+    <t>BENG-BENG ALMOND 35G</t>
+  </si>
+  <si>
+    <t>20044008</t>
+  </si>
+  <si>
+    <t>BENG-BENG MAXX 32G</t>
+  </si>
+  <si>
+    <t>20117108</t>
+  </si>
+  <si>
+    <t>BENG-BENG PCK 3X20G</t>
+  </si>
+  <si>
+    <t>20045176</t>
+  </si>
+  <si>
+    <t>CHA CHA PNUT CHO 20G</t>
+  </si>
+  <si>
+    <t>20112348</t>
+  </si>
+  <si>
+    <t>IDM BLUEBRY D.CHO 45</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20085730</t>
+  </si>
+  <si>
+    <t>IDM CASH MILK CHO 40</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20093638</t>
+  </si>
+  <si>
+    <t>IDM BISC MILK CHO 40</t>
+  </si>
+  <si>
+    <t>20128815</t>
+  </si>
+  <si>
+    <t>IDM GUMMY CHO MF 40G</t>
+  </si>
+  <si>
     <t>20084899</t>
   </si>
   <si>
@@ -115,187 +325,10 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20141002</t>
-  </si>
-  <si>
-    <t>WONHAE MTCHA BRY 30G</t>
-  </si>
-  <si>
-    <t>20139890</t>
-  </si>
-  <si>
-    <t>WNHAE STRW CHEESCAKE</t>
-  </si>
-  <si>
-    <t>20139889</t>
-  </si>
-  <si>
-    <t>WNHAE PISTACHIO CHOC</t>
-  </si>
-  <si>
-    <t>20135198</t>
-  </si>
-  <si>
-    <t>WONHAE YOG.GUM ORI48</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20135661</t>
-  </si>
-  <si>
-    <t>WNHAE GMMY MXD.FRT32</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20083719</t>
-  </si>
-  <si>
-    <t>NANO MILKY COK 12G</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20033392</t>
-  </si>
-  <si>
-    <t>DELFI CHACHA MINIS25</t>
-  </si>
-  <si>
-    <t>20077110</t>
-  </si>
-  <si>
-    <t>CHACHA MINIS HATS 25</t>
-  </si>
-  <si>
-    <t>20122057</t>
-  </si>
-  <si>
-    <t>CHACHA MINIS CAR12.5</t>
-  </si>
-  <si>
-    <t>20140016</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHO PEANUT 37G</t>
-  </si>
-  <si>
-    <t>20140013</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHOC CRSPY 30G</t>
-  </si>
-  <si>
-    <t>20129814</t>
-  </si>
-  <si>
-    <t>MLKITA CNDY BTES 24G</t>
-  </si>
-  <si>
-    <t>20140908</t>
-  </si>
-  <si>
-    <t>MLKITA PUDD STRW 85G</t>
-  </si>
-  <si>
-    <t>20140907</t>
-  </si>
-  <si>
-    <t>MLKITA PUDD MILK 85G</t>
-  </si>
-  <si>
-    <t>20045175</t>
-  </si>
-  <si>
-    <t>CHA CHA MILK CHO 20G</t>
-  </si>
-  <si>
-    <t>20045176</t>
-  </si>
-  <si>
-    <t>CHA CHA PNUT CHO 20G</t>
-  </si>
-  <si>
-    <t>20063093</t>
-  </si>
-  <si>
-    <t>DELFI MALTITOS 26</t>
-  </si>
-  <si>
-    <t>10000418</t>
-  </si>
-  <si>
-    <t>DELFI CHIC CHOC 36G</t>
-  </si>
-  <si>
-    <t>20024539</t>
-  </si>
-  <si>
-    <t>S/Q BITES ALMOND 30G</t>
-  </si>
-  <si>
-    <t>20128815</t>
-  </si>
-  <si>
-    <t>IDM GUMMY CHO MF 40G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140906</t>
-  </si>
-  <si>
-    <t>MILKITA BAR CHOC 15G</t>
-  </si>
-  <si>
-    <t>20140412</t>
-  </si>
-  <si>
-    <t>MILKITA MILKY BAR 15</t>
-  </si>
-  <si>
-    <t>20113490</t>
-  </si>
-  <si>
-    <t>BENG-BENG ALMOND 35G</t>
-  </si>
-  <si>
-    <t>20044008</t>
-  </si>
-  <si>
-    <t>BENG-BENG MAXX 32G</t>
-  </si>
-  <si>
-    <t>20117108</t>
-  </si>
-  <si>
-    <t>BENG-BENG PCK 3X20G</t>
-  </si>
-  <si>
-    <t>20112348</t>
-  </si>
-  <si>
-    <t>IDM BLUEBRY D.CHO 45</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20085730</t>
-  </si>
-  <si>
-    <t>IDM CASH MILK CHO 40</t>
-  </si>
-  <si>
-    <t>20093638</t>
-  </si>
-  <si>
-    <t>IDM BISC MILK CHO 40</t>
+    <t>20065363</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCOLAT 70</t>
   </si>
   <si>
     <t>20046198</t>
@@ -310,6 +343,42 @@
     <t>SNICKERS CHOCO 35G</t>
   </si>
   <si>
+    <t>20142997</t>
+  </si>
+  <si>
+    <t>SNICKERS CHOCO FB</t>
+  </si>
+  <si>
+    <t>20142589</t>
+  </si>
+  <si>
+    <t>DELFI NOCKER BDD2X35</t>
+  </si>
+  <si>
+    <t>20142332</t>
+  </si>
+  <si>
+    <t>LARIST CHOCO EGG 20G</t>
+  </si>
+  <si>
+    <t>20120946</t>
+  </si>
+  <si>
+    <t>KINDER JOY DC COMICS</t>
+  </si>
+  <si>
+    <t>20130547</t>
+  </si>
+  <si>
+    <t>DELFI CHOCO DM 2X25G</t>
+  </si>
+  <si>
+    <t>20134029</t>
+  </si>
+  <si>
+    <t>DELFI TRSURE MLK2X30</t>
+  </si>
+  <si>
     <t>10008315</t>
   </si>
   <si>
@@ -325,34 +394,34 @@
     <t>LMNILO CRNCHY CHO 18</t>
   </si>
   <si>
-    <t>20134029</t>
-  </si>
-  <si>
-    <t>DELFI TRSURE MLK2X30</t>
-  </si>
-  <si>
-    <t>20130547</t>
-  </si>
-  <si>
-    <t>DELFI CHOCO DM 2X25G</t>
-  </si>
-  <si>
     <t>10000757</t>
   </si>
   <si>
     <t>L'AGIE FULL MILK 60G</t>
   </si>
   <si>
-    <t>20120946</t>
-  </si>
-  <si>
-    <t>KINDER JOY DC COMICS</t>
-  </si>
-  <si>
-    <t>20133639</t>
-  </si>
-  <si>
-    <t>DW DARK.CHO ALMND 56</t>
+    <t>20142508</t>
+  </si>
+  <si>
+    <t>DARK WONDER  BDD2X40</t>
+  </si>
+  <si>
+    <t>20062877</t>
+  </si>
+  <si>
+    <t>CADBURY BLCK.FOR 57G</t>
+  </si>
+  <si>
+    <t>20054753</t>
+  </si>
+  <si>
+    <t>CADBURY FRUIT&amp;NUT 52</t>
+  </si>
+  <si>
+    <t>20120257</t>
+  </si>
+  <si>
+    <t>CADBURY HAZELNUT 52G</t>
   </si>
   <si>
     <t>20089666</t>
@@ -361,42 +430,6 @@
     <t>CADBURY CSHW NUT 85G</t>
   </si>
   <si>
-    <t>20062877</t>
-  </si>
-  <si>
-    <t>CADBURY BLCK.FOR 57G</t>
-  </si>
-  <si>
-    <t>20054753</t>
-  </si>
-  <si>
-    <t>CADBURY FRUIT&amp;NUT 52</t>
-  </si>
-  <si>
-    <t>20120257</t>
-  </si>
-  <si>
-    <t>CADBURY HAZELNUT 52G</t>
-  </si>
-  <si>
-    <t>20140883</t>
-  </si>
-  <si>
-    <t>CADBURY BUBBLY 46G</t>
-  </si>
-  <si>
-    <t>20141062</t>
-  </si>
-  <si>
-    <t>SQ CHUNKY CUPID 3X26</t>
-  </si>
-  <si>
-    <t>20141063</t>
-  </si>
-  <si>
-    <t>SQ CSHW BTRFLY 3X22G</t>
-  </si>
-  <si>
     <t>20008798</t>
   </si>
   <si>
@@ -409,6 +442,12 @@
     <t>S/Q CHOCO CASHEW 52G</t>
   </si>
   <si>
+    <t>20124902</t>
+  </si>
+  <si>
+    <t>SQ B2G1 CASHEW 3X52G</t>
+  </si>
+  <si>
     <t>20092545</t>
   </si>
   <si>
@@ -427,9 +466,6 @@
     <t>SQ CHUNKY MINIS 10X8</t>
   </si>
   <si>
-    <t>TG,(E-1B)</t>
-  </si>
-  <si>
     <t>20130159</t>
   </si>
   <si>
@@ -448,30 +484,30 @@
     <t>MILO CHOCO CUBE67.5G</t>
   </si>
   <si>
+    <t>20129562</t>
+  </si>
+  <si>
+    <t>IDM FD STRW CHOC 45G</t>
+  </si>
+  <si>
+    <t>20129561</t>
+  </si>
+  <si>
+    <t>IDM RAISIN CHOCO 60G</t>
+  </si>
+  <si>
+    <t>20129559</t>
+  </si>
+  <si>
+    <t>IDM ALMND CHOCO 60G</t>
+  </si>
+  <si>
     <t>20129560</t>
   </si>
   <si>
     <t>IDM HAZEL CHOCO 60G</t>
   </si>
   <si>
-    <t>20129562</t>
-  </si>
-  <si>
-    <t>IDM FD STRW CHOC 45G</t>
-  </si>
-  <si>
-    <t>20129561</t>
-  </si>
-  <si>
-    <t>IDM RAISIN CHOCO 60G</t>
-  </si>
-  <si>
-    <t>20129559</t>
-  </si>
-  <si>
-    <t>IDM ALMND CHOCO 60G</t>
-  </si>
-  <si>
     <t>20093135</t>
   </si>
   <si>
@@ -502,7 +538,7 @@
     <t>10037013</t>
   </si>
   <si>
-    <t>RELAXA BARLEY MNT108</t>
+    <t>RELAXA BARLEY MNT 81</t>
   </si>
   <si>
     <t>20043035</t>
@@ -511,6 +547,12 @@
     <t>H/WHITE GUM MINT 70G</t>
   </si>
   <si>
+    <t>10032611</t>
+  </si>
+  <si>
+    <t>GARUDA TING2 KCNG125</t>
+  </si>
+  <si>
     <t>10012263</t>
   </si>
   <si>
@@ -574,25 +616,19 @@
     <t>MINTZ CNDY.PPRMNT 99</t>
   </si>
   <si>
-    <t>20136282</t>
-  </si>
-  <si>
-    <t>MILKITA LOLIPOP 3'S</t>
+    <t>20143054</t>
+  </si>
+  <si>
+    <t>FOXS GUM EMOTIS 50</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>20082651</t>
-  </si>
-  <si>
-    <t>BIG BB FLFLY TTFR 11</t>
-  </si>
-  <si>
-    <t>20113106</t>
-  </si>
-  <si>
-    <t>YUPI SWT ARTIFACT 77</t>
+    <t>20142221</t>
+  </si>
+  <si>
+    <t>YUPI CND GMY FANGS90</t>
   </si>
   <si>
     <t>10013885</t>
@@ -619,55 +655,76 @@
     <t>YUPI KISS STRAW 110G</t>
   </si>
   <si>
+    <t>20141954</t>
+  </si>
+  <si>
+    <t>YUPI CRUNCY GUMMY 50</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20141597</t>
+  </si>
+  <si>
+    <t>FRUZZ GUMMY ASORTD36</t>
+  </si>
+  <si>
+    <t>20142223</t>
+  </si>
+  <si>
+    <t>BONCHA CND GUMMY 60G</t>
+  </si>
+  <si>
+    <t>20138897</t>
+  </si>
+  <si>
+    <t>JLO FRIED EGG 78G</t>
+  </si>
+  <si>
+    <t>20129720</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY WLD SFR44</t>
+  </si>
+  <si>
+    <t>10000312</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY GL.STK 45</t>
+  </si>
+  <si>
+    <t>10006540</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY BB.BEAR45</t>
+  </si>
+  <si>
+    <t>10006534</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY KS.STW 45</t>
+  </si>
+  <si>
+    <t>20064920</t>
+  </si>
+  <si>
+    <t>YUPI LITTLE STARS 45</t>
+  </si>
+  <si>
     <t>20140015</t>
   </si>
   <si>
     <t>AMOS BANANA GUMMY 68</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20141597</t>
-  </si>
-  <si>
-    <t>FRUZZ GUMMY ASORTD36</t>
-  </si>
-  <si>
-    <t>20138897</t>
-  </si>
-  <si>
-    <t>JLO FRIED EGG 78G</t>
-  </si>
-  <si>
-    <t>20129720</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY WLD SFR44</t>
-  </si>
-  <si>
-    <t>10000312</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY GL.STK 45</t>
-  </si>
-  <si>
-    <t>10006540</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY BB.BEAR45</t>
-  </si>
-  <si>
-    <t>20064920</t>
-  </si>
-  <si>
-    <t>YUPI LITTLE STARS 45</t>
-  </si>
-  <si>
-    <t>20141954</t>
-  </si>
-  <si>
-    <t>YUPI CRUNCY GUMMY 50</t>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20087289</t>
+  </si>
+  <si>
+    <t>CHP.CHUPS BITES 56G</t>
   </si>
   <si>
     <t>20139394</t>
@@ -676,19 +733,40 @@
     <t>JLO GUMMY BEAR 40G</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>20135995</t>
   </si>
   <si>
     <t>JLO GUMMY BITE 40G</t>
   </si>
   <si>
-    <t>20087289</t>
-  </si>
-  <si>
-    <t>CHP.CHUPS BITES 56G</t>
+    <t>20047250</t>
+  </si>
+  <si>
+    <t>YUPI CALCI BEAN 70G</t>
+  </si>
+  <si>
+    <t>20080530</t>
+  </si>
+  <si>
+    <t>YUPI BIG BURGER 32G</t>
+  </si>
+  <si>
+    <t>20048724</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY PIZZA 23G</t>
+  </si>
+  <si>
+    <t>20136191</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY NOODLE23G</t>
+  </si>
+  <si>
+    <t>20052776</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY B/FRNK 32</t>
   </si>
   <si>
     <t>20139774</t>
@@ -697,42 +775,6 @@
     <t>CH.CHUP ROPES S/C 24</t>
   </si>
   <si>
-    <t>10006534</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY KS.STW 45</t>
-  </si>
-  <si>
-    <t>20080530</t>
-  </si>
-  <si>
-    <t>YUPI BIG BURGER 32G</t>
-  </si>
-  <si>
-    <t>20048724</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY PIZZA 23G</t>
-  </si>
-  <si>
-    <t>20136191</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY NOODLE23G</t>
-  </si>
-  <si>
-    <t>20052776</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY B/FRNK 32</t>
-  </si>
-  <si>
-    <t>20047250</t>
-  </si>
-  <si>
-    <t>YUPI CALCI BEAN 70G</t>
-  </si>
-  <si>
     <t>20138164</t>
   </si>
   <si>
@@ -784,9 +826,6 @@
     <t>YUPI GUMMY KOR BBQ70</t>
   </si>
   <si>
-    <t>,(E-1B)</t>
-  </si>
-  <si>
     <t>10000766</t>
   </si>
   <si>
@@ -802,6 +841,15 @@
     <t>SUGUS STICK BLCRNT30</t>
   </si>
   <si>
+    <t>20129719</t>
+  </si>
+  <si>
+    <t>FROZZ ANGGR MINT 14G</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
     <t>20014081</t>
   </si>
   <si>
@@ -820,12 +868,6 @@
     <t>FROZZ CHERRY MINT 15</t>
   </si>
   <si>
-    <t>20138041</t>
-  </si>
-  <si>
-    <t>FROZZ MANGO BINGSO14</t>
-  </si>
-  <si>
     <t>20067474</t>
   </si>
   <si>
@@ -868,33 +910,33 @@
     <t>MILTON PSTLS LMN16.5</t>
   </si>
   <si>
+    <t>10011038</t>
+  </si>
+  <si>
+    <t>WOODS PEP.EXT/STRG15</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20109048</t>
+  </si>
+  <si>
+    <t>HEXOS MINT 8'S</t>
+  </si>
+  <si>
+    <t>10033024</t>
+  </si>
+  <si>
+    <t>S/M CANDY TLK.AGN 5S</t>
+  </si>
+  <si>
     <t>20099973</t>
   </si>
   <si>
     <t>HMLYA SL CNDY LMN 15</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20109048</t>
-  </si>
-  <si>
-    <t>HEXOS MINT 8'S</t>
-  </si>
-  <si>
-    <t>10011038</t>
-  </si>
-  <si>
-    <t>WOODS PEP.EXT/STRG15</t>
-  </si>
-  <si>
-    <t>10033024</t>
-  </si>
-  <si>
-    <t>S/M CANDY TLK.AGN 5S</t>
-  </si>
-  <si>
     <t>20110265</t>
   </si>
   <si>
@@ -943,13 +985,13 @@
     <t>20016240</t>
   </si>
   <si>
-    <t>FOX'S CRYST.BERIES90</t>
+    <t>FOX'S CRYST.BERIES80</t>
   </si>
   <si>
     <t>10000763</t>
   </si>
   <si>
-    <t>FOX'S CANDY FRUIT 90</t>
+    <t>FOX'S CANDY FRUIT 80</t>
   </si>
   <si>
     <t>10028390</t>
@@ -967,13 +1009,13 @@
     <t>20018396</t>
   </si>
   <si>
-    <t>H/WHITE GUM BTL 44'S</t>
+    <t>H/WHITE GUM BTL 40'S</t>
   </si>
   <si>
     <t>20094668</t>
   </si>
   <si>
-    <t>HPYDNT COOL MINT 28G</t>
+    <t>HPYDNT C/G COOL MINT</t>
   </si>
   <si>
     <t>20138379</t>
@@ -1390,14 +1432,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F157"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1597,15 +1639,15 @@
         <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1622,10 +1664,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1637,7 +1679,7 @@
         <v>15</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1757,7 +1799,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1931,10 +1973,10 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1951,10 +1993,10 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1974,7 +2016,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1994,7 +2036,7 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2014,7 +2056,7 @@
         <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2031,30 +2073,30 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2062,10 +2104,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -2074,7 +2116,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2082,10 +2124,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2094,7 +2136,7 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2102,10 +2144,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2114,7 +2156,7 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2122,10 +2164,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2134,7 +2176,7 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2142,50 +2184,50 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>90</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F39" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2194,18 +2236,18 @@
         <v>21</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2214,10 +2256,10 @@
         <v>21</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2234,10 +2276,10 @@
         <v>21</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2254,18 +2296,18 @@
         <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2274,10 +2316,10 @@
         <v>21</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2291,10 +2333,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2311,10 +2353,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2331,13 +2373,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2351,10 +2393,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2371,10 +2413,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2391,13 +2433,13 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2411,10 +2453,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2431,10 +2473,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2451,10 +2493,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2471,30 +2513,30 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2502,39 +2544,39 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2542,19 +2584,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2562,19 +2604,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2582,19 +2624,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2602,22 +2644,22 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>138</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2631,10 +2673,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2651,10 +2693,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2671,10 +2713,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2691,13 +2733,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2711,13 +2753,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2734,10 +2776,10 @@
         <v>48</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2754,10 +2796,10 @@
         <v>48</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2774,7 +2816,7 @@
         <v>48</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2794,10 +2836,10 @@
         <v>48</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2814,87 +2856,87 @@
         <v>48</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>159</v>
+        <v>48</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>159</v>
+        <v>48</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>159</v>
+        <v>48</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>159</v>
+        <v>48</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2902,39 +2944,39 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>159</v>
+        <v>48</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2951,7 +2993,7 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>4</v>
@@ -2962,16 +3004,16 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>8</v>
@@ -2982,16 +3024,16 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>12</v>
@@ -3002,36 +3044,36 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>18</v>
@@ -3042,56 +3084,56 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>4</v>
@@ -3102,16 +3144,16 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>8</v>
@@ -3122,36 +3164,36 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>15</v>
@@ -3162,16 +3204,16 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>18</v>
@@ -3182,56 +3224,56 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>4</v>
@@ -3242,19 +3284,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3262,19 +3304,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3282,19 +3324,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3302,19 +3344,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3322,19 +3364,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3342,19 +3384,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3371,10 +3413,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3391,10 +3433,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3402,19 +3444,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3422,19 +3464,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3442,19 +3484,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3462,19 +3504,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3482,19 +3524,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3502,19 +3544,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3522,22 +3564,22 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3551,10 +3593,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3571,10 +3613,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3591,10 +3633,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3602,19 +3644,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3622,19 +3664,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3642,19 +3684,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3662,39 +3704,39 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3702,19 +3744,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3722,39 +3764,39 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>257</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3762,19 +3804,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3782,79 +3824,79 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3862,39 +3904,39 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3902,19 +3944,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3922,179 +3964,179 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>280</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4102,19 +4144,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>24</v>
+        <v>188</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4122,22 +4164,22 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
+      <c r="E137" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F137" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4151,70 +4193,70 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>77</v>
+        <v>294</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4222,39 +4264,39 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>273</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4262,19 +4304,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4282,19 +4324,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E145" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4311,13 +4353,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4331,10 +4373,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4351,10 +4393,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4371,13 +4413,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>287</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4391,12 +4433,152 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="F150" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F157" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/CON02D.xlsx
+++ b/E/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="346">
   <si>
     <t/>
   </si>
@@ -100,9 +100,6 @@
     <t>CHA CHA TSUM 2X12.5</t>
   </si>
   <si>
-    <t>TG,(E-1B)</t>
-  </si>
-  <si>
     <t>20097984</t>
   </si>
   <si>
@@ -160,6 +157,15 @@
     <t>10</t>
   </si>
   <si>
+    <t>20143332</t>
+  </si>
+  <si>
+    <t>HIFRUIT GRAPE  25G</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>20033392</t>
   </si>
   <si>
@@ -526,9 +532,6 @@
     <t>KALPA SHRE IT 90G</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>20053360</t>
   </si>
   <si>
@@ -712,13 +715,19 @@
     <t>YUPI LITTLE STARS 45</t>
   </si>
   <si>
+    <t>20143286</t>
+  </si>
+  <si>
+    <t>AMOS MANGO PEELZ PCH</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>20140015</t>
   </si>
   <si>
     <t>AMOS BANANA GUMMY 68</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>20087289</t>
@@ -1432,7 +1441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F157"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1639,15 +1648,15 @@
         <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1664,10 +1673,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1684,10 +1693,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1704,10 +1713,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1724,10 +1733,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1744,10 +1753,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1756,7 +1765,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1764,10 +1773,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1776,7 +1785,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1784,10 +1793,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1796,7 +1805,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1804,19 +1813,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -1836,7 +1845,7 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1856,7 +1865,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1876,7 +1885,7 @@
         <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1896,7 +1905,7 @@
         <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1916,7 +1925,7 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1936,7 +1945,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1956,7 +1965,7 @@
         <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1976,7 +1985,7 @@
         <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1996,7 +2005,7 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2013,10 +2022,10 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2036,7 +2045,7 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2056,7 +2065,7 @@
         <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2076,7 +2085,7 @@
         <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2096,7 +2105,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2113,10 +2122,10 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2136,7 +2145,7 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2156,7 +2165,7 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2176,7 +2185,7 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2196,7 +2205,7 @@
         <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2216,7 +2225,7 @@
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2233,21 +2242,21 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F40" s="1" t="s">
-        <v>93</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2256,18 +2265,18 @@
         <v>21</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2276,10 +2285,10 @@
         <v>21</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2296,10 +2305,10 @@
         <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2316,18 +2325,18 @@
         <v>21</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2336,10 +2345,10 @@
         <v>21</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2356,7 +2365,7 @@
         <v>21</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2376,7 +2385,7 @@
         <v>21</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2396,7 +2405,7 @@
         <v>21</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2416,7 +2425,7 @@
         <v>21</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2433,13 +2442,13 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2456,10 +2465,10 @@
         <v>24</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2476,7 +2485,7 @@
         <v>24</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2496,7 +2505,7 @@
         <v>24</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2516,18 +2525,18 @@
         <v>24</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2536,10 +2545,10 @@
         <v>24</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2553,13 +2562,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2573,13 +2582,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2593,10 +2602,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2613,10 +2622,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2633,10 +2642,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2653,10 +2662,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2673,10 +2682,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2693,10 +2702,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2713,10 +2722,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2733,10 +2742,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2753,10 +2762,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2773,10 +2782,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2793,10 +2802,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2813,10 +2822,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2833,10 +2842,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2853,13 +2862,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2873,13 +2882,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2893,13 +2902,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2913,13 +2922,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2933,13 +2942,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2953,13 +2962,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2973,30 +2982,30 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3004,19 +3013,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3024,19 +3033,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3044,59 +3053,59 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3104,19 +3113,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3124,19 +3133,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3144,19 +3153,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3164,19 +3173,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3184,19 +3193,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3204,19 +3213,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3224,39 +3233,39 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>9</v>
@@ -3264,39 +3273,39 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3304,19 +3313,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3324,19 +3333,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3344,19 +3353,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3364,19 +3373,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3384,19 +3393,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3404,19 +3413,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3424,19 +3433,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3444,19 +3453,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3464,19 +3473,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3484,19 +3493,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3504,19 +3513,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3524,19 +3533,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3544,19 +3553,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3564,19 +3573,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3584,19 +3593,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3604,19 +3613,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3624,19 +3633,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3644,19 +3653,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3664,19 +3673,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3684,19 +3693,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3704,39 +3713,39 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3744,39 +3753,39 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3784,19 +3793,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3804,19 +3813,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3824,19 +3833,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3844,19 +3853,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3864,19 +3873,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3884,19 +3893,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3904,19 +3913,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3924,19 +3933,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3944,19 +3953,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3964,79 +3973,79 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>278</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>9</v>
@@ -4044,99 +4053,99 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>287</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>294</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4144,159 +4153,159 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F136" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>287</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>5</v>
+        <v>297</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4304,19 +4313,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4324,19 +4333,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4344,39 +4353,39 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4384,59 +4393,59 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>287</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4444,39 +4453,39 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>290</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4484,19 +4493,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4504,19 +4513,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4524,19 +4533,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4544,19 +4553,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>188</v>
+        <v>47</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4564,21 +4573,61 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F157" s="1" t="s">
+      <c r="B158" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F159" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/CON02D.xlsx
+++ b/E/CON02D.xlsx
@@ -619,15 +619,21 @@
     <t>MINTZ CNDY.PPRMNT 99</t>
   </si>
   <si>
+    <t>20143521</t>
+  </si>
+  <si>
+    <t>RJN BRY SWEET CDY 40</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>20143054</t>
   </si>
   <si>
     <t>FOXS GUM EMOTIS 50</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>20142221</t>
   </si>
   <si>
@@ -718,16 +724,10 @@
     <t>20143286</t>
   </si>
   <si>
-    <t>AMOS MANGO PEELZ PCH</t>
+    <t>AMOS PEELZ MANGO 65G</t>
   </si>
   <si>
     <t>15</t>
-  </si>
-  <si>
-    <t>20140015</t>
-  </si>
-  <si>
-    <t>AMOS BANANA GUMMY 68</t>
   </si>
   <si>
     <t>20087289</t>
@@ -3422,10 +3422,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3433,19 +3433,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3462,10 +3462,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3482,10 +3482,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3502,10 +3502,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3522,10 +3522,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3542,10 +3542,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3562,10 +3562,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3582,10 +3582,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3602,10 +3602,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3613,19 +3613,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3642,7 +3642,7 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>12</v>
@@ -3662,7 +3662,7 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>15</v>
@@ -3682,7 +3682,7 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>18</v>
@@ -3702,7 +3702,7 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>21</v>
@@ -3722,7 +3722,7 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>24</v>
@@ -3742,7 +3742,7 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>41</v>
@@ -3762,7 +3762,7 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>44</v>
@@ -3782,7 +3782,7 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>47</v>
@@ -3802,7 +3802,7 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>50</v>
